--- a/834_issuer_etl/assets/64357/excel/kpi_summary_64357.xlsx
+++ b/834_issuer_etl/assets/64357/excel/kpi_summary_64357.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subscriber_flag" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="relationship_code" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_type" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_reason" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="maintenance_type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="insurance_type" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rating_area" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="effective_month" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="premium_rating_area" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="premium_effective_month" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_trend" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="enrollee_by_file" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="subscriber_flag" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="relationship_code" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="event_type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="event_reason" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="maintenance_type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="insurance_type" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="rating_area" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="effective_month" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="premium_rating_area" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="premium_effective_month" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="file_trend" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="enrollee_by_file" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,13 +29,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +49,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,12 +57,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,12 +441,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -607,12 +619,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rating_area</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>total_total_premium_amt</t>
         </is>
@@ -753,12 +765,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>effective_month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>total_premium</t>
         </is>
@@ -799,17 +811,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>file_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>enrollee_count</t>
         </is>
@@ -890,12 +902,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -956,12 +968,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>subscriber_flag</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1002,12 +1014,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>relationship_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1058,12 +1070,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>event_type_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1094,12 +1106,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>event_reason_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1130,12 +1142,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>maintenance_type_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1166,12 +1178,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>insurance_type_code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1202,12 +1214,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>rating_area</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
@@ -1348,12 +1360,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>effective_month</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>count</t>
         </is>
